--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,6 +133,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -157,8 +161,12 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>深创100ETF</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -601,7 +609,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -763,6 +771,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -772,7 +783,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -933,6 +944,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -976,7 +990,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1138,6 +1152,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1147,7 +1164,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1309,6 +1326,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1681068.5808443392</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1717781.1968650564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1351,7 +1371,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1513,6 +1533,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1522,7 +1545,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1684,6 +1707,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>522575.55136211542</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>559288.16738283262</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1705,11 +1731,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="160695040"/>
-        <c:axId val="160697344"/>
+        <c:axId val="529086336"/>
+        <c:axId val="529092608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="160695040"/>
+        <c:axId val="529086336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1752,14 +1778,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160697344"/>
+        <c:crossAx val="529092608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="160697344"/>
+        <c:axId val="529092608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1810,7 +1836,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="160695040"/>
+        <c:crossAx val="529086336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2001,7 +2027,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2163,6 +2189,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-18333.497294467583</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-46393.241034391052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2177,8 +2206,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="557061632"/>
-        <c:axId val="557060096"/>
+        <c:axId val="670284800"/>
+        <c:axId val="670283264"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2203,7 +2232,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2365,6 +2394,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2374,7 +2406,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2536,6 +2568,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2552,11 +2587,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557056768"/>
-        <c:axId val="557058304"/>
+        <c:axId val="670279936"/>
+        <c:axId val="670281728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557056768"/>
+        <c:axId val="670279936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2599,14 +2634,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557058304"/>
+        <c:crossAx val="670281728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557058304"/>
+        <c:axId val="670281728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2657,12 +2692,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557056768"/>
+        <c:crossAx val="670279936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="557060096"/>
+        <c:axId val="670283264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2699,12 +2734,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557061632"/>
+        <c:crossAx val="670284800"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="557061632"/>
+        <c:axId val="670284800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2713,7 +2748,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="557060096"/>
+        <c:crossAx val="670283264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2875,7 +2910,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3037,6 +3072,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3051,8 +3089,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="556518400"/>
-        <c:axId val="556516480"/>
+        <c:axId val="547036160"/>
+        <c:axId val="529132160"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3077,7 +3115,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3239,6 +3277,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3248,7 +3289,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3410,6 +3451,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3426,11 +3470,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556513152"/>
-        <c:axId val="556514688"/>
+        <c:axId val="529103872"/>
+        <c:axId val="529130624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556513152"/>
+        <c:axId val="529103872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3473,14 +3517,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556514688"/>
+        <c:crossAx val="529130624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556514688"/>
+        <c:axId val="529130624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3531,12 +3575,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556513152"/>
+        <c:crossAx val="529103872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="556516480"/>
+        <c:axId val="529132160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3573,12 +3617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556518400"/>
+        <c:crossAx val="547036160"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="556518400"/>
+        <c:axId val="547036160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3587,7 +3631,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="556516480"/>
+        <c:crossAx val="529132160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3766,7 +3810,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3928,6 +3972,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3937,7 +3984,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4098,6 +4145,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4141,7 +4191,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4303,6 +4353,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4312,7 +4365,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4474,6 +4527,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1783595.7523900417</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1822259.0783629464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4516,7 +4572,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4678,6 +4734,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4687,7 +4746,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4849,6 +4908,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>561358.82646509632</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>600022.15243800101</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4870,11 +4932,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556592512"/>
-        <c:axId val="556754048"/>
+        <c:axId val="620944384"/>
+        <c:axId val="621361408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556592512"/>
+        <c:axId val="620944384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4917,14 +4979,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556754048"/>
+        <c:crossAx val="621361408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556754048"/>
+        <c:axId val="621361408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4975,7 +5037,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556592512"/>
+        <c:crossAx val="620944384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5166,7 +5228,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5328,6 +5390,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-19017.419881633017</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-24948.75484946607</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5342,8 +5407,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="574261120"/>
-        <c:axId val="556857984"/>
+        <c:axId val="674702848"/>
+        <c:axId val="674701312"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5368,7 +5433,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5530,6 +5595,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5539,7 +5607,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5701,6 +5769,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5717,11 +5788,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556830080"/>
-        <c:axId val="556856448"/>
+        <c:axId val="674500608"/>
+        <c:axId val="674502144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556830080"/>
+        <c:axId val="674500608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5764,14 +5835,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556856448"/>
+        <c:crossAx val="674502144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556856448"/>
+        <c:axId val="674502144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5822,12 +5893,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556830080"/>
+        <c:crossAx val="674500608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="556857984"/>
+        <c:axId val="674701312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5864,12 +5935,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="574261120"/>
+        <c:crossAx val="674702848"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="574261120"/>
+        <c:axId val="674702848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5878,7 +5949,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="556857984"/>
+        <c:crossAx val="674701312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6057,7 +6128,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6219,6 +6290,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6228,7 +6302,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6389,6 +6463,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6432,7 +6509,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6594,6 +6671,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6603,7 +6683,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6765,6 +6845,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1782531.7789662397</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1821371.0623135378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6807,7 +6890,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6969,6 +7052,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6978,7 +7064,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7140,6 +7226,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>556308.84151616995</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>595148.12486346811</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7161,11 +7250,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="598872832"/>
-        <c:axId val="598874368"/>
+        <c:axId val="675286400"/>
+        <c:axId val="675464704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598872832"/>
+        <c:axId val="675286400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7208,14 +7297,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598874368"/>
+        <c:crossAx val="675464704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598874368"/>
+        <c:axId val="675464704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7266,7 +7355,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598872832"/>
+        <c:crossAx val="675286400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7457,7 +7546,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7619,6 +7708,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7633,8 +7725,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="599113088"/>
-        <c:axId val="599111552"/>
+        <c:axId val="758818304"/>
+        <c:axId val="758816768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7659,7 +7751,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7821,6 +7913,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7830,7 +7925,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7992,6 +8087,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8008,11 +8106,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="599097344"/>
-        <c:axId val="599109632"/>
+        <c:axId val="731055616"/>
+        <c:axId val="746405248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="599097344"/>
+        <c:axId val="731055616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8055,14 +8153,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="599109632"/>
+        <c:crossAx val="746405248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="599109632"/>
+        <c:axId val="746405248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8113,12 +8211,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="599097344"/>
+        <c:crossAx val="731055616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="599111552"/>
+        <c:axId val="758816768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8155,12 +8253,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="599113088"/>
+        <c:crossAx val="758818304"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="599113088"/>
+        <c:axId val="758818304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8169,7 +8267,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="599111552"/>
+        <c:crossAx val="758816768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8348,7 +8446,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8510,6 +8608,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8519,7 +8620,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8680,6 +8781,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -8723,7 +8827,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8885,6 +8989,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8894,7 +9001,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9056,6 +9163,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14844133.861885205</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>15173385.354710398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9098,7 +9208,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9260,6 +9370,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9269,7 +9382,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9431,6 +9544,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4881348.482635295</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5210599.9754604883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9452,11 +9568,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="605028736"/>
-        <c:axId val="605031424"/>
+        <c:axId val="759177984"/>
+        <c:axId val="759180288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="605028736"/>
+        <c:axId val="759177984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9499,14 +9615,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="605031424"/>
+        <c:crossAx val="759180288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="605031424"/>
+        <c:axId val="759180288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9557,7 +9673,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="605028736"/>
+        <c:crossAx val="759177984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9748,7 +9864,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9910,6 +10026,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13718784.399138454</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>13615936.237991611</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9924,8 +10043,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="556685184"/>
-        <c:axId val="556683648"/>
+        <c:axId val="669351296"/>
+        <c:axId val="669349760"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9950,7 +10069,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10112,6 +10231,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10121,7 +10243,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10283,6 +10405,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10299,11 +10424,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556680320"/>
-        <c:axId val="556681856"/>
+        <c:axId val="669346432"/>
+        <c:axId val="669348224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556680320"/>
+        <c:axId val="669346432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10346,14 +10471,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556681856"/>
+        <c:crossAx val="669348224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556681856"/>
+        <c:axId val="669348224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10404,12 +10529,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556680320"/>
+        <c:crossAx val="669346432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="556683648"/>
+        <c:axId val="669349760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10446,12 +10571,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556685184"/>
+        <c:crossAx val="669351296"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="556685184"/>
+        <c:axId val="669351296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10460,7 +10585,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="556683648"/>
+        <c:crossAx val="669349760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10639,7 +10764,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10801,6 +10926,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10810,7 +10938,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10971,6 +11099,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11014,7 +11145,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11176,6 +11307,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11185,7 +11319,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11347,6 +11481,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14293429.419919802</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14614742.276310235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11389,7 +11526,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11551,6 +11688,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11560,7 +11700,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11722,6 +11862,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5428717.1338850353</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5750029.9902754687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11743,11 +11886,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556840064"/>
-        <c:axId val="556841600"/>
+        <c:axId val="670259840"/>
+        <c:axId val="670261632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556840064"/>
+        <c:axId val="670259840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11790,14 +11933,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556841600"/>
+        <c:crossAx val="670261632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556841600"/>
+        <c:axId val="670261632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11848,7 +11991,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556840064"/>
+        <c:crossAx val="670259840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12562,7 +12705,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -12693,28 +12836,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -14975,6 +15118,44 @@
       </c>
       <c r="L56" s="14">
         <v>90191.835636928721</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-19540.064695712677</v>
+      </c>
+      <c r="G57" s="15">
+        <v>1510149.1694970026</v>
+      </c>
+      <c r="H57" s="15">
+        <v>1606798.732186906</v>
+      </c>
+      <c r="I57" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J57" s="15">
+        <v>1717781.1968650564</v>
+      </c>
+      <c r="K57" s="15">
+        <v>559288.16738283262</v>
+      </c>
+      <c r="L57" s="14">
+        <v>110982.46467815044</v>
       </c>
     </row>
   </sheetData>
@@ -14993,7 +15174,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15028,13 +15209,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15064,10 +15245,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15088,7 +15269,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -15168,28 +15349,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -18697,6 +18878,71 @@
         <v>128.53526904457513</v>
       </c>
       <c r="U56" s="11">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-24948.75484946607</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-23448.077634855214</v>
+      </c>
+      <c r="G57" s="15">
+        <v>1587520.5731815591</v>
+      </c>
+      <c r="H57" s="15">
+        <v>1689121.9065189324</v>
+      </c>
+      <c r="I57" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J57" s="15">
+        <v>1822259.0783629464</v>
+      </c>
+      <c r="K57" s="15">
+        <v>600022.15243800101</v>
+      </c>
+      <c r="L57" s="14">
+        <v>133137.17184401408</v>
+      </c>
+      <c r="M57" s="23">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="N57" s="23">
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="O57" s="23">
+        <v>1.0713333288828533</v>
+      </c>
+      <c r="P57" s="23">
+        <v>0.88464285929997755</v>
+      </c>
+      <c r="Q57" s="23">
+        <v>0.18669046958287572</v>
+      </c>
+      <c r="R57" s="23">
+        <v>0.10844557342075166</v>
+      </c>
+      <c r="S57" s="9">
+        <v>1.6266836013112747E-3</v>
+      </c>
+      <c r="T57" s="9">
+        <v>114.76753649719217</v>
+      </c>
+      <c r="U57" s="11">
         <v>1.2</v>
       </c>
     </row>
@@ -18716,7 +18962,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -18754,10 +19000,10 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -18790,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -18857,28 +19103,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -21441,6 +21687,50 @@
         <v>-25.623704638394841</v>
       </c>
       <c r="N56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-19540.064695712677</v>
+      </c>
+      <c r="G57" s="15">
+        <v>1598760.1285293053</v>
+      </c>
+      <c r="H57" s="15">
+        <v>1701080.793526842</v>
+      </c>
+      <c r="I57" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J57" s="15">
+        <v>1821371.0623135378</v>
+      </c>
+      <c r="K57" s="15">
+        <v>595148.12486346811</v>
+      </c>
+      <c r="L57" s="14">
+        <v>120290.26878669577</v>
+      </c>
+      <c r="M57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="N57" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21460,7 +21750,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -21495,13 +21785,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -21534,7 +21824,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -21601,28 +21891,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -24185,6 +24475,50 @@
         <v>-25.623704638394841</v>
       </c>
       <c r="N56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="15">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="15">
+        <v>13615936.237991611</v>
+      </c>
+      <c r="H57" s="15">
+        <v>14487356.300059929</v>
+      </c>
+      <c r="I57" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J57" s="15">
+        <v>15173385.354710398</v>
+      </c>
+      <c r="K57" s="15">
+        <v>5210599.9754604883</v>
+      </c>
+      <c r="L57" s="14">
+        <v>686029.05465046817</v>
+      </c>
+      <c r="M57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="N57" s="9">
         <v>1</v>
       </c>
     </row>
@@ -24204,7 +24538,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI56"/>
+  <dimension ref="A1:AI57"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24239,22 +24573,22 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -24284,7 +24618,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -24359,28 +24693,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -27261,6 +27595,56 @@
         <v>-25.623704638394841</v>
       </c>
       <c r="P56" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.75">
+      <c r="A57" s="12">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="13">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="13">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="14">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="14">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="14">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="14">
+        <v>-46393.241034391052</v>
+      </c>
+      <c r="H57" s="15">
+        <v>-43602.669715207558</v>
+      </c>
+      <c r="I57" s="15">
+        <v>13344405.881644664</v>
+      </c>
+      <c r="J57" s="15">
+        <v>14198447.998058312</v>
+      </c>
+      <c r="K57" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L57" s="15">
+        <v>14614742.276310235</v>
+      </c>
+      <c r="M57" s="15">
+        <v>5750029.9902754687</v>
+      </c>
+      <c r="N57" s="14">
+        <v>416294.2782519231</v>
+      </c>
+      <c r="O57" s="9">
+        <v>38.003913332402767</v>
+      </c>
+      <c r="P57" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -174,6 +174,10 @@
   </si>
   <si>
     <t>最低价</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>标志</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -609,7 +613,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -774,6 +778,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -783,7 +790,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -947,6 +954,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -990,7 +1000,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1155,6 +1165,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1164,7 +1177,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1329,6 +1342,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1717781.1968650564</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1729862.4147042707</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1371,7 +1387,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1536,6 +1552,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1545,7 +1564,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1710,6 +1729,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>559288.16738283262</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>571369.38522204687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1731,11 +1753,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529086336"/>
-        <c:axId val="529092608"/>
+        <c:axId val="155880448"/>
+        <c:axId val="155898624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529086336"/>
+        <c:axId val="155880448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1778,14 +1800,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529092608"/>
+        <c:crossAx val="155898624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529092608"/>
+        <c:axId val="155898624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1836,7 +1858,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529086336"/>
+        <c:crossAx val="155880448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2027,7 +2049,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2192,6 +2214,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-46393.241034391052</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-111127.31971233143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2206,8 +2231,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="670284800"/>
-        <c:axId val="670283264"/>
+        <c:axId val="614357248"/>
+        <c:axId val="614355712"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2232,7 +2257,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2397,6 +2422,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2406,7 +2434,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2571,6 +2599,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2587,11 +2618,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="670279936"/>
-        <c:axId val="670281728"/>
+        <c:axId val="614348288"/>
+        <c:axId val="614349824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="670279936"/>
+        <c:axId val="614348288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2634,14 +2665,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670281728"/>
+        <c:crossAx val="614349824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="670281728"/>
+        <c:axId val="614349824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2692,12 +2723,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670279936"/>
+        <c:crossAx val="614348288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="670283264"/>
+        <c:axId val="614355712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2734,12 +2765,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670284800"/>
+        <c:crossAx val="614357248"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="670284800"/>
+        <c:axId val="614357248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2748,7 +2779,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="670283264"/>
+        <c:crossAx val="614355712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2910,7 +2941,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3075,6 +3106,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3089,8 +3123,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="547036160"/>
-        <c:axId val="529132160"/>
+        <c:axId val="568082432"/>
+        <c:axId val="380500608"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3115,7 +3149,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3280,6 +3314,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3289,7 +3326,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3454,6 +3491,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3470,11 +3510,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529103872"/>
-        <c:axId val="529130624"/>
+        <c:axId val="379542144"/>
+        <c:axId val="379552896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529103872"/>
+        <c:axId val="379542144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3517,14 +3557,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529130624"/>
+        <c:crossAx val="379552896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529130624"/>
+        <c:axId val="379552896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3575,12 +3615,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529103872"/>
+        <c:crossAx val="379542144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529132160"/>
+        <c:axId val="380500608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3617,12 +3657,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547036160"/>
+        <c:crossAx val="568082432"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="547036160"/>
+        <c:axId val="568082432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3631,7 +3671,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529132160"/>
+        <c:crossAx val="380500608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3810,7 +3850,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3975,6 +4015,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3984,7 +4027,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4148,6 +4191,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4191,7 +4237,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4356,6 +4402,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4365,7 +4414,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4530,6 +4579,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1822259.0783629464</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1834959.2686860184</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4572,7 +4624,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4737,6 +4789,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4746,7 +4801,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4911,6 +4966,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>600022.15243800101</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>612722.34276107303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4932,11 +4990,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="620944384"/>
-        <c:axId val="621361408"/>
+        <c:axId val="581239552"/>
+        <c:axId val="581241088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="620944384"/>
+        <c:axId val="581239552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4979,14 +5037,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621361408"/>
+        <c:crossAx val="581241088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621361408"/>
+        <c:axId val="581241088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5037,7 +5095,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620944384"/>
+        <c:crossAx val="581239552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5228,7 +5286,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5393,6 +5451,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-24948.75484946607</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5407,8 +5468,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="674702848"/>
-        <c:axId val="674701312"/>
+        <c:axId val="625045504"/>
+        <c:axId val="623110400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5433,7 +5494,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5598,6 +5659,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5607,7 +5671,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5772,6 +5836,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5788,11 +5855,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="674500608"/>
-        <c:axId val="674502144"/>
+        <c:axId val="613212544"/>
+        <c:axId val="623108864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="674500608"/>
+        <c:axId val="613212544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5835,14 +5902,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="674502144"/>
+        <c:crossAx val="623108864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="674502144"/>
+        <c:axId val="623108864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5893,12 +5960,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="674500608"/>
+        <c:crossAx val="613212544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="674701312"/>
+        <c:axId val="623110400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5935,12 +6002,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="674702848"/>
+        <c:crossAx val="625045504"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="674702848"/>
+        <c:axId val="625045504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5949,7 +6016,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="674701312"/>
+        <c:crossAx val="623110400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6128,7 +6195,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6293,6 +6360,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6302,7 +6372,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6466,6 +6536,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6509,7 +6582,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6674,6 +6747,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6683,7 +6759,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6848,6 +6924,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1821371.0623135378</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1834161.1692616125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6890,7 +6969,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7055,6 +7134,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7064,7 +7146,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7229,6 +7311,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>595148.12486346811</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>607938.23181154276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7250,11 +7335,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="675286400"/>
-        <c:axId val="675464704"/>
+        <c:axId val="659358848"/>
+        <c:axId val="659360768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="675286400"/>
+        <c:axId val="659358848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7297,14 +7382,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="675464704"/>
+        <c:crossAx val="659360768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="675464704"/>
+        <c:axId val="659360768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7355,7 +7440,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="675286400"/>
+        <c:crossAx val="659358848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7546,7 +7631,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7711,6 +7796,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7725,8 +7813,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="758818304"/>
-        <c:axId val="758816768"/>
+        <c:axId val="662861696"/>
+        <c:axId val="662672896"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7751,7 +7839,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7916,6 +8004,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7925,7 +8016,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8090,6 +8181,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8106,11 +8200,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="731055616"/>
-        <c:axId val="746405248"/>
+        <c:axId val="662485248"/>
+        <c:axId val="662671360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="731055616"/>
+        <c:axId val="662485248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8153,14 +8247,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="746405248"/>
+        <c:crossAx val="662671360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="746405248"/>
+        <c:axId val="662671360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8211,12 +8305,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="731055616"/>
+        <c:crossAx val="662485248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="758816768"/>
+        <c:axId val="662672896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8253,12 +8347,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="758818304"/>
+        <c:crossAx val="662861696"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="758818304"/>
+        <c:axId val="662861696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8267,7 +8361,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="758816768"/>
+        <c:crossAx val="662672896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8446,7 +8540,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8611,6 +8705,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8620,7 +8717,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8784,6 +8881,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -8827,7 +8927,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8992,6 +9092,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9001,7 +9104,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9166,6 +9269,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15173385.354710398</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>15282313.065362198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9208,7 +9314,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9373,6 +9479,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9382,7 +9491,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9547,6 +9656,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5210599.9754604883</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5319527.6861122884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9568,11 +9680,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="759177984"/>
-        <c:axId val="759180288"/>
+        <c:axId val="679302656"/>
+        <c:axId val="679304576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="759177984"/>
+        <c:axId val="679302656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9615,14 +9727,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="759180288"/>
+        <c:crossAx val="679304576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="759180288"/>
+        <c:axId val="679304576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9673,7 +9785,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="759177984"/>
+        <c:crossAx val="679302656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9864,7 +9976,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10029,6 +10141,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>13615936.237991611</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>13494676.161662014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10043,8 +10158,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="669351296"/>
-        <c:axId val="669349760"/>
+        <c:axId val="612231808"/>
+        <c:axId val="612230272"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10069,7 +10184,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10234,6 +10349,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10243,7 +10361,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10408,6 +10526,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10424,11 +10545,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="669346432"/>
-        <c:axId val="669348224"/>
+        <c:axId val="612226944"/>
+        <c:axId val="612228480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="669346432"/>
+        <c:axId val="612226944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10471,14 +10592,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669348224"/>
+        <c:crossAx val="612228480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="669348224"/>
+        <c:axId val="612228480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10529,12 +10650,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669346432"/>
+        <c:crossAx val="612226944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="669349760"/>
+        <c:axId val="612230272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10571,12 +10692,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669351296"/>
+        <c:crossAx val="612231808"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="669351296"/>
+        <c:axId val="612231808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10585,7 +10706,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="669349760"/>
+        <c:crossAx val="612230272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10764,7 +10885,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10929,6 +11050,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10938,7 +11062,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11102,6 +11226,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11145,7 +11272,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11310,6 +11437,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11319,7 +11449,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11484,6 +11614,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14614742.276310235</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14721497.739709083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11526,7 +11659,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11691,6 +11824,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11700,7 +11836,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11865,6 +12001,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5750029.9902754687</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5856785.4536743164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11886,11 +12025,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="670259840"/>
-        <c:axId val="670261632"/>
+        <c:axId val="612345728"/>
+        <c:axId val="612347264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="670259840"/>
+        <c:axId val="612345728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11933,14 +12072,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670261632"/>
+        <c:crossAx val="612347264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="670261632"/>
+        <c:axId val="612347264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11991,7 +12130,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670259840"/>
+        <c:crossAx val="612345728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12705,7 +12844,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15158,6 +15297,44 @@
         <v>110982.46467815044</v>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="15">
+        <v>1489011.355676573</v>
+      </c>
+      <c r="H58" s="15">
+        <v>1596220.2130461792</v>
+      </c>
+      <c r="I58" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J58" s="15">
+        <v>1729862.4147042707</v>
+      </c>
+      <c r="K58" s="15">
+        <v>571369.38522204687</v>
+      </c>
+      <c r="L58" s="14">
+        <v>133642.20165809162</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15174,7 +15351,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -18946,6 +19123,71 @@
         <v>1.2</v>
       </c>
     </row>
+    <row r="58" spans="1:21" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="15">
+        <v>1566382.7593611295</v>
+      </c>
+      <c r="H58" s="15">
+        <v>1679162.3598620631</v>
+      </c>
+      <c r="I58" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J58" s="15">
+        <v>1834959.2686860184</v>
+      </c>
+      <c r="K58" s="15">
+        <v>612722.34276107303</v>
+      </c>
+      <c r="L58" s="14">
+        <v>155796.90882395528</v>
+      </c>
+      <c r="M58" s="23">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="N58" s="23">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="O58" s="23">
+        <v>1.0756666660308838</v>
+      </c>
+      <c r="P58" s="23">
+        <v>0.904595238821847</v>
+      </c>
+      <c r="Q58" s="23">
+        <v>0.17107142720903679</v>
+      </c>
+      <c r="R58" s="23">
+        <v>0.11863264907785012</v>
+      </c>
+      <c r="S58" s="9">
+        <v>1.7794897361677517E-3</v>
+      </c>
+      <c r="T58" s="9">
+        <v>96.135101952006963</v>
+      </c>
+      <c r="U58" s="11">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -18962,7 +19204,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19000,7 +19242,7 @@
         <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
         <v>27</v>
@@ -19036,7 +19278,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -21731,6 +21973,50 @@
         <v>38.003913332402767</v>
       </c>
       <c r="N57" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="15">
+        <v>1577622.3147088757</v>
+      </c>
+      <c r="H58" s="15">
+        <v>1691211.1634949755</v>
+      </c>
+      <c r="I58" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J58" s="15">
+        <v>1834161.1692616125</v>
+      </c>
+      <c r="K58" s="15">
+        <v>607938.23181154276</v>
+      </c>
+      <c r="L58" s="14">
+        <v>142950.00576663695</v>
+      </c>
+      <c r="M58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="N58" s="9">
         <v>1</v>
       </c>
     </row>
@@ -21750,7 +22036,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24522,6 +24808,50 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:14" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="15">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="15">
+        <v>13494676.161662014</v>
+      </c>
+      <c r="H58" s="15">
+        <v>14466293.205648409</v>
+      </c>
+      <c r="I58" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J58" s="15">
+        <v>15282313.065362198</v>
+      </c>
+      <c r="K58" s="15">
+        <v>5319527.6861122884</v>
+      </c>
+      <c r="L58" s="14">
+        <v>816019.85971378826</v>
+      </c>
+      <c r="M58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -24538,7 +24868,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI57"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24585,10 +24915,10 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -27645,6 +27975,56 @@
         <v>38.003913332402767</v>
       </c>
       <c r="P57" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.75">
+      <c r="A58" s="12">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="13">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="13">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="14">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="14">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="14">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="14">
+        <v>-111127.31971233143</v>
+      </c>
+      <c r="H58" s="15">
+        <v>-103663.54192557483</v>
+      </c>
+      <c r="I58" s="15">
+        <v>13240742.339719089</v>
+      </c>
+      <c r="J58" s="15">
+        <v>14194076.141744828</v>
+      </c>
+      <c r="K58" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L58" s="15">
+        <v>14721497.739709083</v>
+      </c>
+      <c r="M58" s="15">
+        <v>5856785.4536743164</v>
+      </c>
+      <c r="N58" s="14">
+        <v>527421.59796425456</v>
+      </c>
+      <c r="O58" s="9">
+        <v>-130.04693515337254</v>
+      </c>
+      <c r="P58" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -161,23 +161,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>最高价</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>最低价</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>标志</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -613,7 +601,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -781,6 +769,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -790,7 +781,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -957,6 +948,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1000,7 +994,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1168,6 +1162,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1177,7 +1174,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1345,6 +1342,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1729862.4147042707</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1734329.4800120019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1387,7 +1387,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1555,6 +1555,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1564,7 +1567,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1732,6 +1735,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>571369.38522204687</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>575836.45052977814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1753,11 +1759,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="155880448"/>
-        <c:axId val="155898624"/>
+        <c:axId val="105726336"/>
+        <c:axId val="105727872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="155880448"/>
+        <c:axId val="105726336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1800,14 +1806,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155898624"/>
+        <c:crossAx val="105727872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="155898624"/>
+        <c:axId val="105727872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1858,7 +1864,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="155880448"/>
+        <c:crossAx val="105726336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2049,7 +2055,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2217,6 +2223,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-111127.31971233143</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-56932.913434554059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2231,8 +2240,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="614357248"/>
-        <c:axId val="614355712"/>
+        <c:axId val="522917760"/>
+        <c:axId val="522916224"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2257,7 +2266,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2425,6 +2434,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2434,7 +2446,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2602,6 +2614,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2618,11 +2633,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="614348288"/>
-        <c:axId val="614349824"/>
+        <c:axId val="522577024"/>
+        <c:axId val="522578560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="614348288"/>
+        <c:axId val="522577024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2665,14 +2680,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614349824"/>
+        <c:crossAx val="522578560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614349824"/>
+        <c:axId val="522578560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2723,12 +2738,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614348288"/>
+        <c:crossAx val="522577024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="614355712"/>
+        <c:axId val="522916224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2765,12 +2780,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614357248"/>
+        <c:crossAx val="522917760"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="614357248"/>
+        <c:axId val="522917760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2779,7 +2794,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="614355712"/>
+        <c:crossAx val="522916224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2941,7 +2956,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3109,6 +3124,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3123,8 +3141,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="568082432"/>
-        <c:axId val="380500608"/>
+        <c:axId val="529454208"/>
+        <c:axId val="529419648"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3149,7 +3167,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3317,6 +3335,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3326,7 +3347,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3494,6 +3515,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3510,11 +3534,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="379542144"/>
-        <c:axId val="379552896"/>
+        <c:axId val="446759680"/>
+        <c:axId val="529418112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="379542144"/>
+        <c:axId val="446759680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3557,14 +3581,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="379552896"/>
+        <c:crossAx val="529418112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="379552896"/>
+        <c:axId val="529418112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3615,12 +3639,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="379542144"/>
+        <c:crossAx val="446759680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="380500608"/>
+        <c:axId val="529419648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3657,12 +3681,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568082432"/>
+        <c:crossAx val="529454208"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="568082432"/>
+        <c:axId val="529454208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3671,7 +3695,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="380500608"/>
+        <c:crossAx val="529419648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3850,7 +3874,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4018,6 +4042,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4027,7 +4054,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4194,6 +4221,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4237,7 +4267,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4405,6 +4435,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4414,7 +4447,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4582,6 +4615,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1834959.2686860184</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1839658.4498281199</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4624,7 +4660,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4792,6 +4828,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4801,7 +4840,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4969,6 +5008,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>612722.34276107303</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>617421.52390317456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4990,11 +5032,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="581239552"/>
-        <c:axId val="581241088"/>
+        <c:axId val="530675584"/>
+        <c:axId val="530677120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="581239552"/>
+        <c:axId val="530675584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5037,14 +5079,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581241088"/>
+        <c:crossAx val="530677120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="581241088"/>
+        <c:axId val="530677120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5095,7 +5137,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="581239552"/>
+        <c:crossAx val="530675584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5286,7 +5328,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5454,6 +5496,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5468,8 +5513,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="625045504"/>
-        <c:axId val="623110400"/>
+        <c:axId val="531577472"/>
+        <c:axId val="531574784"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5494,7 +5539,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5662,6 +5707,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5671,7 +5719,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5839,6 +5887,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5855,11 +5906,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="613212544"/>
-        <c:axId val="623108864"/>
+        <c:axId val="530993152"/>
+        <c:axId val="530995072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="613212544"/>
+        <c:axId val="530993152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5902,14 +5953,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623108864"/>
+        <c:crossAx val="530995072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623108864"/>
+        <c:axId val="530995072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5960,12 +6011,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="613212544"/>
+        <c:crossAx val="530993152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="623110400"/>
+        <c:axId val="531574784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6002,12 +6053,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625045504"/>
+        <c:crossAx val="531577472"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="625045504"/>
+        <c:axId val="531577472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6016,7 +6067,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="623110400"/>
+        <c:crossAx val="531574784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6195,7 +6246,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6363,6 +6414,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6372,7 +6426,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6539,6 +6593,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6582,7 +6639,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6750,6 +6807,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6759,7 +6819,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6927,6 +6987,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1834161.1692616125</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1838894.0693055724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6969,7 +7032,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7137,6 +7200,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7146,7 +7212,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7314,6 +7380,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>607938.23181154276</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>612671.13185550272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7335,11 +7404,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="659358848"/>
-        <c:axId val="659360768"/>
+        <c:axId val="616109952"/>
+        <c:axId val="616129280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="659358848"/>
+        <c:axId val="616109952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7382,14 +7451,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="659360768"/>
+        <c:crossAx val="616129280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="659360768"/>
+        <c:axId val="616129280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7440,7 +7509,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="659358848"/>
+        <c:crossAx val="616109952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7631,7 +7700,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7799,6 +7868,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7813,8 +7885,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="662861696"/>
-        <c:axId val="662672896"/>
+        <c:axId val="625953408"/>
+        <c:axId val="625950080"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7839,7 +7911,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8007,6 +8079,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8016,7 +8091,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8184,6 +8259,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8200,11 +8278,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662485248"/>
-        <c:axId val="662671360"/>
+        <c:axId val="625946624"/>
+        <c:axId val="625948160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662485248"/>
+        <c:axId val="625946624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8247,14 +8325,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662671360"/>
+        <c:crossAx val="625948160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662671360"/>
+        <c:axId val="625948160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8305,12 +8383,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662485248"/>
+        <c:crossAx val="625946624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="662672896"/>
+        <c:axId val="625950080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8347,12 +8425,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662861696"/>
+        <c:crossAx val="625953408"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="662861696"/>
+        <c:axId val="625953408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8361,7 +8439,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662672896"/>
+        <c:crossAx val="625950080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8540,7 +8618,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8708,6 +8786,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8717,7 +8798,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8884,6 +8965,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -8927,7 +9011,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9095,6 +9179,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9104,7 +9191,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9272,6 +9359,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>15282313.065362198</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>15322797.376976756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9314,7 +9404,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9482,6 +9572,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9491,7 +9584,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9659,6 +9752,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5319527.6861122884</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5360011.9977268465</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9680,11 +9776,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="679302656"/>
-        <c:axId val="679304576"/>
+        <c:axId val="626025216"/>
+        <c:axId val="626027520"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="679302656"/>
+        <c:axId val="626025216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9727,14 +9823,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679304576"/>
+        <c:crossAx val="626027520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="679304576"/>
+        <c:axId val="626027520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9785,7 +9881,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="679302656"/>
+        <c:crossAx val="626025216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9976,7 +10072,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10144,6 +10240,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>13494676.161662014</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>13383113.112385772</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10158,8 +10257,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="612231808"/>
-        <c:axId val="612230272"/>
+        <c:axId val="522119424"/>
+        <c:axId val="522117888"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10184,7 +10283,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10352,6 +10451,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10361,7 +10463,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10529,6 +10631,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10545,11 +10650,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="612226944"/>
-        <c:axId val="612228480"/>
+        <c:axId val="522110464"/>
+        <c:axId val="522112000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="612226944"/>
+        <c:axId val="522110464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10592,14 +10697,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612228480"/>
+        <c:crossAx val="522112000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="612228480"/>
+        <c:axId val="522112000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10650,12 +10755,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612226944"/>
+        <c:crossAx val="522110464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="612230272"/>
+        <c:axId val="522117888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10692,12 +10797,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612231808"/>
+        <c:crossAx val="522119424"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="612231808"/>
+        <c:axId val="522119424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10706,7 +10811,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="612230272"/>
+        <c:crossAx val="522117888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10885,7 +10990,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11053,6 +11158,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11062,7 +11170,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11229,6 +11337,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11272,7 +11383,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11440,6 +11551,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11449,7 +11563,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11617,6 +11731,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14721497.739709083</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14761220.244530071</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11659,7 +11776,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11827,6 +11944,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11836,7 +11956,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12004,6 +12124,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5856785.4536743164</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5896507.958495304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12025,11 +12148,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="612345728"/>
-        <c:axId val="612347264"/>
+        <c:axId val="522540544"/>
+        <c:axId val="522542080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="612345728"/>
+        <c:axId val="522540544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12072,14 +12195,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612347264"/>
+        <c:crossAx val="522542080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="612347264"/>
+        <c:axId val="522542080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12130,7 +12253,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="612345728"/>
+        <c:crossAx val="522540544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12844,7 +12967,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15335,6 +15458,44 @@
         <v>133642.20165809162</v>
       </c>
     </row>
+    <row r="59" spans="1:12" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="15">
+        <v>1468764.6441986805</v>
+      </c>
+      <c r="H59" s="15">
+        <v>1578922.0625497375</v>
+      </c>
+      <c r="I59" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J59" s="15">
+        <v>1734329.4800120019</v>
+      </c>
+      <c r="K59" s="15">
+        <v>575836.45052977814</v>
+      </c>
+      <c r="L59" s="14">
+        <v>155407.41746226454</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15351,7 +15512,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM58"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15386,13 +15547,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15422,10 +15583,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15446,7 +15607,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -19185,6 +19346,71 @@
         <v>96.135101952006963</v>
       </c>
       <c r="U58" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="15">
+        <v>1546136.047883237</v>
+      </c>
+      <c r="H59" s="15">
+        <v>1662096.3251999917</v>
+      </c>
+      <c r="I59" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J59" s="15">
+        <v>1839658.4498281199</v>
+      </c>
+      <c r="K59" s="15">
+        <v>617421.52390317456</v>
+      </c>
+      <c r="L59" s="14">
+        <v>177562.12462812819</v>
+      </c>
+      <c r="M59" s="23">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="N59" s="23">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="O59" s="23">
+        <v>1.071333368619283</v>
+      </c>
+      <c r="P59" s="23">
+        <v>0.92366667020888549</v>
+      </c>
+      <c r="Q59" s="23">
+        <v>0.14766669841039748</v>
+      </c>
+      <c r="R59" s="23">
+        <v>0.1233809505190168</v>
+      </c>
+      <c r="S59" s="9">
+        <v>1.850714257785252E-3</v>
+      </c>
+      <c r="T59" s="9">
+        <v>79.789031607240162</v>
+      </c>
+      <c r="U59" s="11">
         <v>1</v>
       </c>
     </row>
@@ -19204,7 +19430,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19245,7 +19471,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -19278,7 +19504,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -22017,6 +22243,50 @@
         <v>-130.04693515337254</v>
       </c>
       <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="15">
+        <v>1557375.6032309833</v>
+      </c>
+      <c r="H59" s="15">
+        <v>1674178.8477347626</v>
+      </c>
+      <c r="I59" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J59" s="15">
+        <v>1838894.0693055724</v>
+      </c>
+      <c r="K59" s="15">
+        <v>612671.13185550272</v>
+      </c>
+      <c r="L59" s="14">
+        <v>164715.22157080987</v>
+      </c>
+      <c r="M59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="N59" s="9">
         <v>1</v>
       </c>
     </row>
@@ -22036,7 +22306,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22074,10 +22344,10 @@
         <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -22110,7 +22380,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -24849,6 +25119,50 @@
         <v>-130.04693515337254</v>
       </c>
       <c r="N58" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="15">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="15">
+        <v>13383113.112385772</v>
+      </c>
+      <c r="H59" s="15">
+        <v>14386847.233971268</v>
+      </c>
+      <c r="I59" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J59" s="15">
+        <v>15322797.376976756</v>
+      </c>
+      <c r="K59" s="15">
+        <v>5360011.9977268465</v>
+      </c>
+      <c r="L59" s="14">
+        <v>935950.14300548914</v>
+      </c>
+      <c r="M59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="N59" s="9">
         <v>1</v>
       </c>
     </row>
@@ -24868,7 +25182,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI58"/>
+  <dimension ref="A1:AI59"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -24906,19 +25220,19 @@
         <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -24948,7 +25262,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -28025,6 +28339,56 @@
         <v>-130.04693515337254</v>
       </c>
       <c r="P58" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.75">
+      <c r="A59" s="12">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="13">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="13">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="14">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="14">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="14">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="14">
+        <v>-56932.913434554059</v>
+      </c>
+      <c r="H59" s="15">
+        <v>-52960.847357380524</v>
+      </c>
+      <c r="I59" s="15">
+        <v>13187781.492361708</v>
+      </c>
+      <c r="J59" s="15">
+        <v>14176865.733131262</v>
+      </c>
+      <c r="K59" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L59" s="15">
+        <v>14761220.244530071</v>
+      </c>
+      <c r="M59" s="15">
+        <v>5896507.958495304</v>
+      </c>
+      <c r="N59" s="14">
+        <v>584354.51139880856</v>
+      </c>
+      <c r="O59" s="9">
+        <v>38.965935849742465</v>
+      </c>
+      <c r="P59" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="30">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -130,10 +130,6 @@
   </si>
   <si>
     <t>回收资金</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -601,7 +597,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -772,6 +768,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -781,7 +780,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -951,6 +950,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -994,7 +996,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1165,6 +1167,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1174,7 +1179,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1345,6 +1350,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1734329.4800120019</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1694672.7323658499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1387,7 +1395,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1558,6 +1566,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1567,7 +1578,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1738,6 +1749,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>575836.45052977814</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>536179.7028836261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1759,11 +1773,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="105726336"/>
-        <c:axId val="105727872"/>
+        <c:axId val="363804544"/>
+        <c:axId val="363806080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="105726336"/>
+        <c:axId val="363804544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1806,14 +1820,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105727872"/>
+        <c:crossAx val="363806080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="105727872"/>
+        <c:axId val="363806080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1864,7 +1878,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="105726336"/>
+        <c:crossAx val="363804544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2055,7 +2069,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2226,6 +2240,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-56932.913434554059</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-37743.814809844756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2240,8 +2257,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522917760"/>
-        <c:axId val="522916224"/>
+        <c:axId val="526313344"/>
+        <c:axId val="526311808"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2266,7 +2283,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2437,6 +2454,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2446,7 +2466,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2617,6 +2637,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2633,11 +2656,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522577024"/>
-        <c:axId val="522578560"/>
+        <c:axId val="526296192"/>
+        <c:axId val="526297728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522577024"/>
+        <c:axId val="526296192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2680,14 +2703,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522578560"/>
+        <c:crossAx val="526297728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522578560"/>
+        <c:axId val="526297728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2738,12 +2761,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522577024"/>
+        <c:crossAx val="526296192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522916224"/>
+        <c:axId val="526311808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2780,12 +2803,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522917760"/>
+        <c:crossAx val="526313344"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522917760"/>
+        <c:axId val="526313344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2794,7 +2817,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522916224"/>
+        <c:crossAx val="526311808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2956,7 +2979,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3127,6 +3150,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3141,8 +3167,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529454208"/>
-        <c:axId val="529419648"/>
+        <c:axId val="476619904"/>
+        <c:axId val="440667520"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3167,7 +3193,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3338,6 +3364,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3347,7 +3376,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3518,6 +3547,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3534,11 +3566,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="446759680"/>
-        <c:axId val="529418112"/>
+        <c:axId val="376604928"/>
+        <c:axId val="427587456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="446759680"/>
+        <c:axId val="376604928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3581,14 +3613,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529418112"/>
+        <c:crossAx val="427587456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529418112"/>
+        <c:axId val="427587456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3639,12 +3671,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="446759680"/>
+        <c:crossAx val="376604928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529419648"/>
+        <c:axId val="440667520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3681,12 +3713,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529454208"/>
+        <c:crossAx val="476619904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529454208"/>
+        <c:axId val="476619904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3695,7 +3727,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529419648"/>
+        <c:crossAx val="440667520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3874,7 +3906,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4045,6 +4077,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4054,7 +4089,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4224,6 +4259,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4267,7 +4305,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4438,6 +4476,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4447,7 +4488,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4618,6 +4659,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1839658.4498281199</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1797912.668896025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4660,7 +4704,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4831,6 +4875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4840,7 +4887,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5011,6 +5058,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>617421.52390317456</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>575675.74297107966</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5032,11 +5082,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530675584"/>
-        <c:axId val="530677120"/>
+        <c:axId val="529075200"/>
+        <c:axId val="529093376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530675584"/>
+        <c:axId val="529075200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5079,14 +5129,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530677120"/>
+        <c:crossAx val="529093376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530677120"/>
+        <c:axId val="529093376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5137,7 +5187,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530675584"/>
+        <c:crossAx val="529075200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5328,7 +5378,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5499,6 +5549,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5513,8 +5566,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="531577472"/>
-        <c:axId val="531574784"/>
+        <c:axId val="529500032"/>
+        <c:axId val="529498496"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5539,7 +5592,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5710,6 +5763,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5719,7 +5775,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5890,6 +5946,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5906,11 +5965,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530993152"/>
-        <c:axId val="530995072"/>
+        <c:axId val="529416960"/>
+        <c:axId val="529418880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530993152"/>
+        <c:axId val="529416960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5953,14 +6012,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530995072"/>
+        <c:crossAx val="529418880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530995072"/>
+        <c:axId val="529418880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6011,12 +6070,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530993152"/>
+        <c:crossAx val="529416960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="531574784"/>
+        <c:axId val="529498496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6053,12 +6112,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531577472"/>
+        <c:crossAx val="529500032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="531577472"/>
+        <c:axId val="529500032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6067,7 +6126,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="531574784"/>
+        <c:crossAx val="529498496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6246,7 +6305,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6417,6 +6476,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6426,7 +6488,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6596,6 +6658,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6639,7 +6704,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6810,6 +6875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6819,7 +6887,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6990,6 +7058,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1838894.0693055724</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1796844.8195966107</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7032,7 +7103,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7203,6 +7274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7212,7 +7286,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7383,6 +7457,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>612671.13185550272</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>570621.88214654103</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7404,11 +7481,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="616109952"/>
-        <c:axId val="616129280"/>
+        <c:axId val="576569728"/>
+        <c:axId val="576571264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="616109952"/>
+        <c:axId val="576569728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7451,14 +7528,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616129280"/>
+        <c:crossAx val="576571264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="616129280"/>
+        <c:axId val="576571264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7509,7 +7586,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616109952"/>
+        <c:crossAx val="576569728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7700,7 +7777,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7871,6 +7948,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7885,8 +7965,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="625953408"/>
-        <c:axId val="625950080"/>
+        <c:axId val="576631936"/>
+        <c:axId val="576628992"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7911,7 +7991,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8082,6 +8162,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8091,7 +8174,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8262,6 +8345,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8278,11 +8364,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="625946624"/>
-        <c:axId val="625948160"/>
+        <c:axId val="576595456"/>
+        <c:axId val="576627072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="625946624"/>
+        <c:axId val="576595456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8325,14 +8411,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625948160"/>
+        <c:crossAx val="576627072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="625948160"/>
+        <c:axId val="576627072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8383,12 +8469,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625946624"/>
+        <c:crossAx val="576595456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="625950080"/>
+        <c:axId val="576628992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8425,12 +8511,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625953408"/>
+        <c:crossAx val="576631936"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="625953408"/>
+        <c:axId val="576631936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8439,7 +8525,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="625950080"/>
+        <c:crossAx val="576628992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8618,7 +8704,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8789,6 +8875,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8798,7 +8887,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8968,6 +9057,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9011,7 +9103,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9182,6 +9274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9191,7 +9286,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9362,6 +9457,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>15322797.376976756</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14961452.391233759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9404,7 +9502,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9575,6 +9673,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9584,7 +9685,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9755,6 +9856,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5360011.9977268465</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4998667.0119838491</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9776,11 +9880,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="626025216"/>
-        <c:axId val="626027520"/>
+        <c:axId val="576785792"/>
+        <c:axId val="576804352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="626025216"/>
+        <c:axId val="576785792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9823,14 +9927,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="626027520"/>
+        <c:crossAx val="576804352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="626027520"/>
+        <c:axId val="576804352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9881,7 +9985,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="626025216"/>
+        <c:crossAx val="576785792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10072,7 +10176,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10243,6 +10347,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>13383113.112385772</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13309711.249315169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10257,8 +10364,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522119424"/>
-        <c:axId val="522117888"/>
+        <c:axId val="526108928"/>
+        <c:axId val="526107392"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10283,7 +10390,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10454,6 +10561,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10463,7 +10573,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10634,6 +10744,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10650,11 +10763,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522110464"/>
-        <c:axId val="522112000"/>
+        <c:axId val="526099968"/>
+        <c:axId val="526101504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522110464"/>
+        <c:axId val="526099968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10697,14 +10810,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522112000"/>
+        <c:crossAx val="526101504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522112000"/>
+        <c:axId val="526101504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10755,12 +10868,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522110464"/>
+        <c:crossAx val="526099968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522117888"/>
+        <c:axId val="526107392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10797,12 +10910,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522119424"/>
+        <c:crossAx val="526108928"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522119424"/>
+        <c:axId val="526108928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10811,7 +10924,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522117888"/>
+        <c:crossAx val="526107392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10990,7 +11103,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11161,6 +11274,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11170,7 +11286,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11340,6 +11456,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11383,7 +11502,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11554,6 +11673,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11563,7 +11685,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11734,6 +11856,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14761220.244530071</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14405149.226126362</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11776,7 +11901,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11947,6 +12072,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11956,7 +12084,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12127,6 +12255,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5896507.958495304</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5540436.9400915951</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12148,11 +12279,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522540544"/>
-        <c:axId val="522542080"/>
+        <c:axId val="526267904"/>
+        <c:axId val="526269440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522540544"/>
+        <c:axId val="526267904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12195,14 +12326,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522542080"/>
+        <c:crossAx val="526269440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522542080"/>
+        <c:axId val="526269440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12253,7 +12384,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522540544"/>
+        <c:crossAx val="526267904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12967,7 +13098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13098,28 +13229,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -15494,6 +15625,44 @@
       </c>
       <c r="L59" s="14">
         <v>155407.41746226454</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="15">
+        <v>1452131.6110652217</v>
+      </c>
+      <c r="H60" s="15">
+        <v>1521833.896544558</v>
+      </c>
+      <c r="I60" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J60" s="15">
+        <v>1694672.7323658499</v>
+      </c>
+      <c r="K60" s="15">
+        <v>536179.7028836261</v>
+      </c>
+      <c r="L60" s="14">
+        <v>172838.83582129193</v>
       </c>
     </row>
   </sheetData>
@@ -15512,7 +15681,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM59"/>
+  <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15547,7 +15716,7 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -15583,10 +15752,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15607,7 +15776,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -15687,28 +15856,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="16" t="s">
+      <c r="X3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="16" t="s">
+      <c r="Y3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -19411,6 +19580,71 @@
         <v>79.789031607240162</v>
       </c>
       <c r="U59" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="15">
+        <v>1529503.0147497782</v>
+      </c>
+      <c r="H60" s="15">
+        <v>1602919.1259088696</v>
+      </c>
+      <c r="I60" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J60" s="15">
+        <v>1797912.668896025</v>
+      </c>
+      <c r="K60" s="15">
+        <v>575675.74297107966</v>
+      </c>
+      <c r="L60" s="14">
+        <v>194993.54298715558</v>
+      </c>
+      <c r="M60" s="23">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="N60" s="23">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="O60" s="23">
+        <v>1.0603333314259846</v>
+      </c>
+      <c r="P60" s="23">
+        <v>0.94423809789475943</v>
+      </c>
+      <c r="Q60" s="23">
+        <v>0.11609523353122519</v>
+      </c>
+      <c r="R60" s="23">
+        <v>0.11939455619474655</v>
+      </c>
+      <c r="S60" s="9">
+        <v>1.7909183429211982E-3</v>
+      </c>
+      <c r="T60" s="9">
+        <v>64.824414798198021</v>
+      </c>
+      <c r="U60" s="11">
         <v>1</v>
       </c>
     </row>
@@ -19430,7 +19664,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19504,7 +19738,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -19571,28 +19805,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -22287,6 +22521,50 @@
         <v>38.965935849742465</v>
       </c>
       <c r="N59" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="15">
+        <v>1540742.5700975244</v>
+      </c>
+      <c r="H60" s="15">
+        <v>1614698.1796667734</v>
+      </c>
+      <c r="I60" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J60" s="15">
+        <v>1796844.8195966107</v>
+      </c>
+      <c r="K60" s="15">
+        <v>570621.88214654103</v>
+      </c>
+      <c r="L60" s="14">
+        <v>182146.63992983726</v>
+      </c>
+      <c r="M60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="N60" s="9">
         <v>1</v>
       </c>
     </row>
@@ -22306,7 +22584,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22341,7 +22619,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -22380,7 +22658,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -22447,28 +22725,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="16" t="s">
+      <c r="S3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="W3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -25163,6 +25441,50 @@
         <v>38.965935849742465</v>
       </c>
       <c r="N59" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="15">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="15">
+        <v>13309711.249315169</v>
+      </c>
+      <c r="H60" s="15">
+        <v>13948577.097340312</v>
+      </c>
+      <c r="I60" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J60" s="15">
+        <v>14961452.391233759</v>
+      </c>
+      <c r="K60" s="15">
+        <v>4998667.0119838491</v>
+      </c>
+      <c r="L60" s="14">
+        <v>1012875.2938934478</v>
+      </c>
+      <c r="M60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="N60" s="9">
         <v>1</v>
       </c>
     </row>
@@ -25182,7 +25504,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AI60"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25217,7 +25539,7 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -25229,10 +25551,10 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -25262,7 +25584,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -25337,28 +25659,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="16" t="s">
+      <c r="T3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="16" t="s">
+      <c r="V3" s="16" t="s">
         <v>22</v>
-      </c>
-      <c r="V3" s="16" t="s">
-        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -28389,6 +28711,56 @@
         <v>38.965935849742465</v>
       </c>
       <c r="P59" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="12.75">
+      <c r="A60" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="13">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="13">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="14">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="14">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="14">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="14">
+        <v>-37743.814809844756</v>
+      </c>
+      <c r="H60" s="15">
+        <v>-36015.091221200484</v>
+      </c>
+      <c r="I60" s="15">
+        <v>13151766.401140507</v>
+      </c>
+      <c r="J60" s="15">
+        <v>13783050.899917709</v>
+      </c>
+      <c r="K60" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L60" s="15">
+        <v>14405149.226126362</v>
+      </c>
+      <c r="M60" s="15">
+        <v>5540436.9400915951</v>
+      </c>
+      <c r="N60" s="14">
+        <v>622098.32620865328</v>
+      </c>
+      <c r="O60" s="9">
+        <v>-89.784897005371036</v>
+      </c>
+      <c r="P60" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -154,6 +154,10 @@
   </si>
   <si>
     <t>年化收益率</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -597,7 +601,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -771,6 +775,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -780,7 +787,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -953,6 +960,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -996,7 +1006,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1170,6 +1180,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1179,7 +1192,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1353,6 +1366,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1694672.7323658499</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1881997.8085183678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1395,7 +1411,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1569,6 +1585,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1578,7 +1597,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1752,6 +1771,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>536179.7028836261</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>723504.77903614403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1773,11 +1795,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="363804544"/>
-        <c:axId val="363806080"/>
+        <c:axId val="467460096"/>
+        <c:axId val="467462016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="363804544"/>
+        <c:axId val="467460096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1820,14 +1842,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="363806080"/>
+        <c:crossAx val="467462016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="363806080"/>
+        <c:axId val="467462016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1878,7 +1900,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="363804544"/>
+        <c:crossAx val="467460096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2069,7 +2091,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2243,6 +2265,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-37743.814809844756</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-102248.30313182416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2257,8 +2282,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="526313344"/>
-        <c:axId val="526311808"/>
+        <c:axId val="528681216"/>
+        <c:axId val="528679680"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2283,7 +2308,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2457,6 +2482,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2466,7 +2494,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2640,6 +2668,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2656,11 +2687,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526296192"/>
-        <c:axId val="526297728"/>
+        <c:axId val="513353216"/>
+        <c:axId val="513354752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526296192"/>
+        <c:axId val="513353216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2703,14 +2734,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526297728"/>
+        <c:crossAx val="513354752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526297728"/>
+        <c:axId val="513354752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2761,12 +2792,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526296192"/>
+        <c:crossAx val="513353216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="526311808"/>
+        <c:axId val="528679680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2803,12 +2834,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526313344"/>
+        <c:crossAx val="528681216"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="526313344"/>
+        <c:axId val="528681216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2817,7 +2848,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="526311808"/>
+        <c:crossAx val="528679680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2979,7 +3010,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3153,6 +3184,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3167,8 +3201,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="476619904"/>
-        <c:axId val="440667520"/>
+        <c:axId val="527324288"/>
+        <c:axId val="527278464"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3193,7 +3227,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3367,6 +3401,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3376,7 +3413,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3550,6 +3587,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3566,11 +3606,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="376604928"/>
-        <c:axId val="427587456"/>
+        <c:axId val="513386752"/>
+        <c:axId val="522857472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="376604928"/>
+        <c:axId val="513386752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3613,14 +3653,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427587456"/>
+        <c:crossAx val="522857472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="427587456"/>
+        <c:axId val="522857472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3671,12 +3711,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="376604928"/>
+        <c:crossAx val="513386752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="440667520"/>
+        <c:axId val="527278464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3713,12 +3753,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="476619904"/>
+        <c:crossAx val="527324288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="476619904"/>
+        <c:axId val="527324288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3727,7 +3767,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="440667520"/>
+        <c:crossAx val="527278464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3906,7 +3946,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4080,6 +4120,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4089,7 +4132,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4262,6 +4305,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4305,7 +4351,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4479,6 +4525,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4488,7 +4537,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4662,6 +4711,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1797912.668896025</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1995218.6613627363</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4704,7 +4756,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4878,6 +4930,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4887,7 +4942,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5061,6 +5116,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>575675.74297107966</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>772981.73543779086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5082,11 +5140,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529075200"/>
-        <c:axId val="529093376"/>
+        <c:axId val="562552832"/>
+        <c:axId val="562554752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529075200"/>
+        <c:axId val="562552832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5129,14 +5187,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529093376"/>
+        <c:crossAx val="562554752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529093376"/>
+        <c:axId val="562554752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5187,7 +5245,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529075200"/>
+        <c:crossAx val="562552832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5378,7 +5436,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5552,6 +5610,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5566,8 +5627,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529500032"/>
-        <c:axId val="529498496"/>
+        <c:axId val="601043328"/>
+        <c:axId val="598653568"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5592,7 +5653,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5766,6 +5827,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5775,7 +5839,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5949,6 +6013,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5965,11 +6032,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529416960"/>
-        <c:axId val="529418880"/>
+        <c:axId val="596244352"/>
+        <c:axId val="598554112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529416960"/>
+        <c:axId val="596244352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6012,14 +6079,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529418880"/>
+        <c:crossAx val="598554112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529418880"/>
+        <c:axId val="598554112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6070,12 +6137,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529416960"/>
+        <c:crossAx val="596244352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529498496"/>
+        <c:axId val="598653568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6112,12 +6179,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529500032"/>
+        <c:crossAx val="601043328"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529500032"/>
+        <c:axId val="601043328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6126,7 +6193,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529498496"/>
+        <c:crossAx val="598653568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6305,7 +6372,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6479,6 +6546,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6488,7 +6558,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6661,6 +6731,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6704,7 +6777,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6878,6 +6951,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6887,7 +6963,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7061,6 +7137,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1796844.8195966107</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1995600.7154642211</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7103,7 +7182,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7277,6 +7356,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7286,7 +7368,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7460,6 +7542,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>570621.88214654103</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>769377.77801415138</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7481,11 +7566,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576569728"/>
-        <c:axId val="576571264"/>
+        <c:axId val="604125824"/>
+        <c:axId val="604144768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576569728"/>
+        <c:axId val="604125824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7528,14 +7613,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576571264"/>
+        <c:crossAx val="604144768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576571264"/>
+        <c:axId val="604144768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7586,7 +7671,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576569728"/>
+        <c:crossAx val="604125824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7777,7 +7862,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7951,6 +8036,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7965,8 +8053,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="576631936"/>
-        <c:axId val="576628992"/>
+        <c:axId val="604340992"/>
+        <c:axId val="604224128"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7991,7 +8079,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8165,6 +8253,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8174,7 +8265,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8348,6 +8439,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8364,11 +8458,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576595456"/>
-        <c:axId val="576627072"/>
+        <c:axId val="604215552"/>
+        <c:axId val="604221440"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576595456"/>
+        <c:axId val="604215552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8411,14 +8505,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576627072"/>
+        <c:crossAx val="604221440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576627072"/>
+        <c:axId val="604221440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8469,12 +8563,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576595456"/>
+        <c:crossAx val="604215552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="576628992"/>
+        <c:axId val="604224128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8511,12 +8605,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576631936"/>
+        <c:crossAx val="604340992"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="576631936"/>
+        <c:axId val="604340992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8525,7 +8619,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="576628992"/>
+        <c:crossAx val="604224128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8704,7 +8798,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8878,6 +8972,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8887,7 +8984,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9060,6 +9157,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9103,7 +9203,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9277,6 +9377,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9286,7 +9389,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9460,6 +9563,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14961452.391233759</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16678406.043607632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9502,7 +9608,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9676,6 +9782,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9685,7 +9794,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9859,6 +9968,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4998667.0119838491</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6715620.6643577218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9880,11 +9992,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="576785792"/>
-        <c:axId val="576804352"/>
+        <c:axId val="467581184"/>
+        <c:axId val="467595264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="576785792"/>
+        <c:axId val="467581184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9927,14 +10039,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576804352"/>
+        <c:crossAx val="467595264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="576804352"/>
+        <c:axId val="467595264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9985,7 +10097,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="576785792"/>
+        <c:crossAx val="467581184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10176,7 +10288,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10350,6 +10462,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>13309711.249315169</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>13078659.210298697</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10364,8 +10479,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="526108928"/>
-        <c:axId val="526107392"/>
+        <c:axId val="489114240"/>
+        <c:axId val="489112704"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10390,7 +10505,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10564,6 +10679,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10573,7 +10691,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10747,6 +10865,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10763,11 +10884,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526099968"/>
-        <c:axId val="526101504"/>
+        <c:axId val="489105280"/>
+        <c:axId val="489106816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526099968"/>
+        <c:axId val="489105280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10810,14 +10931,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526101504"/>
+        <c:crossAx val="489106816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526101504"/>
+        <c:axId val="489106816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10868,12 +10989,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526099968"/>
+        <c:crossAx val="489105280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="526107392"/>
+        <c:axId val="489112704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10910,12 +11031,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526108928"/>
+        <c:crossAx val="489114240"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="526108928"/>
+        <c:axId val="489114240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10924,7 +11045,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="526107392"/>
+        <c:crossAx val="489112704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11103,7 +11224,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11277,6 +11398,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11286,7 +11410,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11459,6 +11583,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11502,7 +11629,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11676,6 +11803,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11685,7 +11815,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11859,6 +11989,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14405149.226126362</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16101727.982391117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11901,7 +12034,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12075,6 +12208,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12084,7 +12220,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12258,6 +12394,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5540436.9400915951</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7237015.6963563506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12279,11 +12418,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526267904"/>
-        <c:axId val="526269440"/>
+        <c:axId val="489133952"/>
+        <c:axId val="489135488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526267904"/>
+        <c:axId val="489133952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12326,14 +12465,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526269440"/>
+        <c:crossAx val="489135488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526269440"/>
+        <c:axId val="489135488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12384,7 +12523,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526267904"/>
+        <c:crossAx val="489133952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13098,7 +13237,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15665,6 +15804,44 @@
         <v>172838.83582129193</v>
       </c>
     </row>
+    <row r="61" spans="1:12" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="15">
+        <v>1424285.4577023056</v>
+      </c>
+      <c r="H61" s="15">
+        <v>1676384.0489142279</v>
+      </c>
+      <c r="I61" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J61" s="15">
+        <v>1881997.8085183678</v>
+      </c>
+      <c r="K61" s="15">
+        <v>723504.77903614403</v>
+      </c>
+      <c r="L61" s="14">
+        <v>205613.75960413984</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -15681,7 +15858,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM60"/>
+  <dimension ref="A1:AM61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15716,7 +15893,7 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -15752,10 +15929,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15776,7 +15953,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -19645,6 +19822,71 @@
         <v>64.824414798198021</v>
       </c>
       <c r="U60" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="15">
+        <v>1501656.8613868621</v>
+      </c>
+      <c r="H61" s="15">
+        <v>1767450.1945927327</v>
+      </c>
+      <c r="I61" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J61" s="15">
+        <v>1995218.6613627363</v>
+      </c>
+      <c r="K61" s="15">
+        <v>772981.73543779086</v>
+      </c>
+      <c r="L61" s="14">
+        <v>227768.46677000349</v>
+      </c>
+      <c r="M61" s="23">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="N61" s="23">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="O61" s="23">
+        <v>1.1330000162124634</v>
+      </c>
+      <c r="P61" s="23">
+        <v>0.9662142892678578</v>
+      </c>
+      <c r="Q61" s="23">
+        <v>0.16678572694460558</v>
+      </c>
+      <c r="R61" s="23">
+        <v>0.11951701130185809</v>
+      </c>
+      <c r="S61" s="9">
+        <v>1.7927551695278712E-3</v>
+      </c>
+      <c r="T61" s="9">
+        <v>93.033187007085431</v>
+      </c>
+      <c r="U61" s="11">
         <v>1</v>
       </c>
     </row>
@@ -19664,7 +19906,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19699,7 +19941,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -19738,7 +19980,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -22565,6 +22807,50 @@
         <v>-89.784897005371036</v>
       </c>
       <c r="N60" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="15">
+        <v>1512896.4167346084</v>
+      </c>
+      <c r="H61" s="15">
+        <v>1780679.1517515359</v>
+      </c>
+      <c r="I61" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J61" s="15">
+        <v>1995600.7154642211</v>
+      </c>
+      <c r="K61" s="15">
+        <v>769377.77801415138</v>
+      </c>
+      <c r="L61" s="14">
+        <v>214921.56371268517</v>
+      </c>
+      <c r="M61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="N61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -22584,7 +22870,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22658,7 +22944,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -25485,6 +25771,50 @@
         <v>-89.784897005371036</v>
       </c>
       <c r="N60" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="15">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="15">
+        <v>13078659.210298697</v>
+      </c>
+      <c r="H61" s="15">
+        <v>15393582.489215072</v>
+      </c>
+      <c r="I61" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J61" s="15">
+        <v>16678406.043607632</v>
+      </c>
+      <c r="K61" s="15">
+        <v>6715620.6643577218</v>
+      </c>
+      <c r="L61" s="14">
+        <v>1284823.5543925592</v>
+      </c>
+      <c r="M61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="N61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -25504,7 +25834,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI60"/>
+  <dimension ref="A1:AI61"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25551,10 +25881,10 @@
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -25584,7 +25914,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -28761,6 +29091,56 @@
         <v>-89.784897005371036</v>
       </c>
       <c r="P60" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="12.75">
+      <c r="A61" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="13">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="13">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="14">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="14">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="14">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="14">
+        <v>-102248.30313182416</v>
+      </c>
+      <c r="H61" s="15">
+        <v>-86871.961899015572</v>
+      </c>
+      <c r="I61" s="15">
+        <v>13064894.439241491</v>
+      </c>
+      <c r="J61" s="15">
+        <v>15377381.35305064</v>
+      </c>
+      <c r="K61" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L61" s="15">
+        <v>16101727.982391117</v>
+      </c>
+      <c r="M61" s="15">
+        <v>7237015.6963563506</v>
+      </c>
+      <c r="N61" s="14">
+        <v>724346.6293404774</v>
+      </c>
+      <c r="O61" s="9">
+        <v>95.218135798121537</v>
+      </c>
+      <c r="P61" s="9">
         <v>1</v>
       </c>
     </row>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(CCI)cn.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="33">
   <si>
     <t>CCI</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -133,6 +133,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -157,8 +161,12 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>深创100ETF</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>最高价</t>
@@ -601,7 +609,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -778,6 +786,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -787,7 +798,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -963,6 +974,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -1006,7 +1020,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1183,6 +1197,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1192,7 +1209,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1369,6 +1386,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1881997.8085183678</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1978849.1612350328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1411,7 +1431,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1588,6 +1608,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1597,7 +1620,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1774,6 +1797,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>723504.77903614403</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>820356.13175280904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1795,11 +1821,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467460096"/>
-        <c:axId val="467462016"/>
+        <c:axId val="375147520"/>
+        <c:axId val="401486592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467460096"/>
+        <c:axId val="375147520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1842,14 +1868,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467462016"/>
+        <c:crossAx val="401486592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467462016"/>
+        <c:axId val="401486592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1900,7 +1926,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467460096"/>
+        <c:crossAx val="375147520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2091,7 +2117,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2268,6 +2294,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-102248.30313182416</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-273879.41101316386</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2282,8 +2311,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="528681216"/>
-        <c:axId val="528679680"/>
+        <c:axId val="472415232"/>
+        <c:axId val="472413696"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2308,7 +2337,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2485,6 +2514,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2494,7 +2526,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2671,6 +2703,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2687,11 +2722,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="513353216"/>
-        <c:axId val="513354752"/>
+        <c:axId val="472406272"/>
+        <c:axId val="472412160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="513353216"/>
+        <c:axId val="472406272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2734,14 +2769,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="513354752"/>
+        <c:crossAx val="472412160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="513354752"/>
+        <c:axId val="472412160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2792,12 +2827,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="513353216"/>
+        <c:crossAx val="472406272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="528679680"/>
+        <c:axId val="472413696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2834,12 +2869,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528681216"/>
+        <c:crossAx val="472415232"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="528681216"/>
+        <c:axId val="472415232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2848,7 +2883,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528679680"/>
+        <c:crossAx val="472413696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3010,7 +3045,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3187,6 +3222,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3201,8 +3239,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="527324288"/>
-        <c:axId val="527278464"/>
+        <c:axId val="427095552"/>
+        <c:axId val="427094016"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3227,7 +3265,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3404,6 +3442,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3413,7 +3454,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -3590,6 +3631,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3606,11 +3650,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="513386752"/>
-        <c:axId val="522857472"/>
+        <c:axId val="401518976"/>
+        <c:axId val="401520512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="513386752"/>
+        <c:axId val="401518976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3653,14 +3697,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522857472"/>
+        <c:crossAx val="401520512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522857472"/>
+        <c:axId val="401520512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3711,12 +3755,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="513386752"/>
+        <c:crossAx val="401518976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="527278464"/>
+        <c:axId val="427094016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3753,12 +3797,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527324288"/>
+        <c:crossAx val="427095552"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="527324288"/>
+        <c:axId val="427095552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3767,7 +3811,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="527278464"/>
+        <c:crossAx val="427094016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3946,7 +3990,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4123,6 +4167,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4132,7 +4179,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4308,6 +4355,9 @@
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1222236.9259249454</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1222236.9259249454</c:v>
                 </c:pt>
               </c:numCache>
@@ -4351,7 +4401,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4528,6 +4578,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4537,7 +4590,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4714,6 +4767,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1995218.6613627363</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2097331.2663571048</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4756,7 +4812,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4933,6 +4989,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4942,7 +5001,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5119,6 +5178,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>772981.73543779086</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>875094.34043215937</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5140,11 +5202,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="562552832"/>
-        <c:axId val="562554752"/>
+        <c:axId val="438244480"/>
+        <c:axId val="438921088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="562552832"/>
+        <c:axId val="438244480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5187,14 +5249,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562554752"/>
+        <c:crossAx val="438921088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="562554752"/>
+        <c:axId val="438921088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5245,7 +5307,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562552832"/>
+        <c:crossAx val="438244480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5436,7 +5498,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5613,6 +5675,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-43268.840010340289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5627,8 +5692,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="601043328"/>
-        <c:axId val="598653568"/>
+        <c:axId val="548006912"/>
+        <c:axId val="548005376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5653,7 +5718,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5830,6 +5895,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5839,7 +5907,7 @@
               <c:f>'模型二 (1)PE副本计算CCI月线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6016,6 +6084,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6032,11 +6103,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="596244352"/>
-        <c:axId val="598554112"/>
+        <c:axId val="547804672"/>
+        <c:axId val="547806592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="596244352"/>
+        <c:axId val="547804672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6079,14 +6150,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598554112"/>
+        <c:crossAx val="547806592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598554112"/>
+        <c:axId val="547806592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6137,12 +6208,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="596244352"/>
+        <c:crossAx val="547804672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="598653568"/>
+        <c:axId val="548005376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6179,12 +6250,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="601043328"/>
+        <c:crossAx val="548006912"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="601043328"/>
+        <c:axId val="548006912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6193,7 +6264,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="598653568"/>
+        <c:crossAx val="548005376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6372,7 +6443,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6549,6 +6620,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6558,7 +6632,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6734,6 +6808,9 @@
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1226222.9374500697</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1226222.9374500697</c:v>
                 </c:pt>
               </c:numCache>
@@ -6777,7 +6854,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6954,6 +7031,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6963,7 +7043,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7140,6 +7220,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1995600.7154642211</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2098477.6097613247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7182,7 +7265,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7359,6 +7442,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7368,7 +7454,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7545,6 +7631,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>769377.77801415138</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>872254.67231125501</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7566,11 +7655,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="604125824"/>
-        <c:axId val="604144768"/>
+        <c:axId val="556909696"/>
+        <c:axId val="556911232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="604125824"/>
+        <c:axId val="556909696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7613,14 +7702,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="604144768"/>
+        <c:crossAx val="556911232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="604144768"/>
+        <c:axId val="556911232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7671,7 +7760,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="604125824"/>
+        <c:crossAx val="556909696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7862,7 +7951,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8039,6 +8128,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-43268.840010340289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8053,8 +8145,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="604340992"/>
-        <c:axId val="604224128"/>
+        <c:axId val="656609280"/>
+        <c:axId val="654231424"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8079,7 +8171,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8256,6 +8348,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8265,7 +8360,7 @@
               <c:f>'模型二 (1)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8442,6 +8537,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8458,11 +8556,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="604215552"/>
-        <c:axId val="604221440"/>
+        <c:axId val="654091776"/>
+        <c:axId val="654229888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="604215552"/>
+        <c:axId val="654091776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8505,14 +8603,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="604221440"/>
+        <c:crossAx val="654229888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="604221440"/>
+        <c:axId val="654229888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8563,12 +8661,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="604215552"/>
+        <c:crossAx val="654091776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="604224128"/>
+        <c:axId val="654231424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8605,12 +8703,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="604340992"/>
+        <c:crossAx val="656609280"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="604340992"/>
+        <c:axId val="656609280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8619,7 +8717,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="604224128"/>
+        <c:crossAx val="654231424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8798,7 +8896,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8975,6 +9073,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8984,7 +9085,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9160,6 +9261,9 @@
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9962785.3792499099</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9962785.3792499099</c:v>
                 </c:pt>
               </c:numCache>
@@ -9203,7 +9307,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9380,6 +9484,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9389,7 +9496,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9566,6 +9673,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>16678406.043607632</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>17567754.333578344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9608,7 +9718,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9785,6 +9895,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9794,7 +9907,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9971,6 +10084,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6715620.6643577218</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7604968.9543284345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9992,11 +10108,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467581184"/>
-        <c:axId val="467595264"/>
+        <c:axId val="656642048"/>
+        <c:axId val="656644352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467581184"/>
+        <c:axId val="656642048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10039,14 +10155,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467595264"/>
+        <c:crossAx val="656644352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467595264"/>
+        <c:axId val="656644352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10097,7 +10213,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467581184"/>
+        <c:crossAx val="656642048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10288,7 +10404,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10465,6 +10581,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>13078659.210298697</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12761408.348849542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10479,8 +10598,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="489114240"/>
-        <c:axId val="489112704"/>
+        <c:axId val="657036032"/>
+        <c:axId val="656931456"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10505,7 +10624,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10682,6 +10801,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10691,7 +10813,7 @@
               <c:f>'模型二 (2)PE副本计算CCI日线'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10868,6 +10990,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10884,11 +11009,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="489105280"/>
-        <c:axId val="489106816"/>
+        <c:axId val="656660352"/>
+        <c:axId val="656661888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="489105280"/>
+        <c:axId val="656660352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10931,14 +11056,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489106816"/>
+        <c:crossAx val="656661888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="489106816"/>
+        <c:axId val="656661888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10989,12 +11114,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489105280"/>
+        <c:crossAx val="656660352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="489112704"/>
+        <c:axId val="656931456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11031,12 +11156,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489114240"/>
+        <c:crossAx val="657036032"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="489114240"/>
+        <c:axId val="657036032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11045,7 +11170,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="489112704"/>
+        <c:crossAx val="656931456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11224,7 +11349,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11401,6 +11526,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11410,7 +11538,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11586,6 +11714,9 @@
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>8864712.2860347666</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>8864712.2860347666</c:v>
                 </c:pt>
               </c:numCache>
@@ -11629,7 +11760,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11806,6 +11937,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11815,7 +11949,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11992,6 +12126,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>16101727.982391117</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16990140.268494405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12034,7 +12171,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12211,6 +12348,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12220,7 +12360,7 @@
               <c:f>'模型二 (2)PE副本成交量计算CCI日线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12397,6 +12537,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>7237015.6963563506</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>8125427.9824596383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12418,11 +12561,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="489133952"/>
-        <c:axId val="489135488"/>
+        <c:axId val="472308352"/>
+        <c:axId val="472387968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="489133952"/>
+        <c:axId val="472308352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12465,14 +12608,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489135488"/>
+        <c:crossAx val="472387968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="489135488"/>
+        <c:axId val="472387968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12523,7 +12666,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489133952"/>
+        <c:crossAx val="472308352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13237,7 +13380,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -13368,28 +13511,28 @@
       </c>
       <c r="M3" s="9"/>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -15840,6 +15983,44 @@
       </c>
       <c r="L61" s="14">
         <v>205613.75960413984</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="15">
+        <v>1395323.7175117971</v>
+      </c>
+      <c r="H62" s="15">
+        <v>1737178.0349556094</v>
+      </c>
+      <c r="I62" s="15">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J62" s="15">
+        <v>1978849.1612350328</v>
+      </c>
+      <c r="K62" s="15">
+        <v>820356.13175280904</v>
+      </c>
+      <c r="L62" s="14">
+        <v>241671.12627942342</v>
       </c>
     </row>
   </sheetData>
@@ -15858,7 +16039,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -15893,13 +16074,13 @@
   <sheetData>
     <row r="1" spans="1:39" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -15929,10 +16110,10 @@
         <v>18</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -15953,7 +16134,7 @@
         <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="14.1" customHeight="1">
@@ -16033,28 +16214,28 @@
       <c r="R3" s="23"/>
       <c r="S3" s="9"/>
       <c r="V3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="AB3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE3" s="24">
         <v>44561</v>
@@ -19888,6 +20069,71 @@
       </c>
       <c r="U61" s="11">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-43268.840010340289</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-34754.088228610344</v>
+      </c>
+      <c r="G62" s="15">
+        <v>1466902.7731582518</v>
+      </c>
+      <c r="H62" s="15">
+        <v>1826293.9595767609</v>
+      </c>
+      <c r="I62" s="15">
+        <v>1222236.9259249454</v>
+      </c>
+      <c r="J62" s="15">
+        <v>2097331.2663571048</v>
+      </c>
+      <c r="K62" s="15">
+        <v>875094.34043215937</v>
+      </c>
+      <c r="L62" s="14">
+        <v>271037.30678034376</v>
+      </c>
+      <c r="M62" s="23">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="N62" s="23">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="O62" s="23">
+        <v>1.2263333400090535</v>
+      </c>
+      <c r="P62" s="23">
+        <v>0.9948571466264271</v>
+      </c>
+      <c r="Q62" s="23">
+        <v>0.23147619338262637</v>
+      </c>
+      <c r="R62" s="23">
+        <v>0.11985034480386848</v>
+      </c>
+      <c r="S62" s="9">
+        <v>1.7977551720580272E-3</v>
+      </c>
+      <c r="T62" s="9">
+        <v>128.75846332158676</v>
+      </c>
+      <c r="U62" s="11">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -19906,7 +20152,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -19941,7 +20187,7 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B1" s="25" t="s">
         <v>8</v>
@@ -19980,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -20047,28 +20293,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -22852,6 +23098,50 @@
       </c>
       <c r="N61" s="9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-43268.840010340289</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-34754.088228610344</v>
+      </c>
+      <c r="G62" s="15">
+        <v>1478142.328505998</v>
+      </c>
+      <c r="H62" s="15">
+        <v>1840287.2060382995</v>
+      </c>
+      <c r="I62" s="15">
+        <v>1226222.9374500697</v>
+      </c>
+      <c r="J62" s="15">
+        <v>2098477.6097613247</v>
+      </c>
+      <c r="K62" s="15">
+        <v>872254.67231125501</v>
+      </c>
+      <c r="L62" s="14">
+        <v>258190.40372302546</v>
+      </c>
+      <c r="M62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="N62" s="9">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -22870,7 +23160,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -22905,13 +23195,13 @@
   <sheetData>
     <row r="1" spans="1:33" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
@@ -22944,7 +23234,7 @@
         <v>0</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:33" ht="14.1" customHeight="1">
@@ -23011,28 +23301,28 @@
         <v>1</v>
       </c>
       <c r="P3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="24">
         <v>44561</v>
@@ -25816,6 +26106,50 @@
       </c>
       <c r="N61" s="9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>-394977.32401696721</v>
+      </c>
+      <c r="F62" s="15">
+        <v>-317250.86144915438</v>
+      </c>
+      <c r="G62" s="15">
+        <v>12761408.348849542</v>
+      </c>
+      <c r="H62" s="15">
+        <v>15887953.455168817</v>
+      </c>
+      <c r="I62" s="15">
+        <v>9962785.3792499099</v>
+      </c>
+      <c r="J62" s="15">
+        <v>17567754.333578344</v>
+      </c>
+      <c r="K62" s="15">
+        <v>7604968.9543284345</v>
+      </c>
+      <c r="L62" s="14">
+        <v>1679800.8784095263</v>
+      </c>
+      <c r="M62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="N62" s="9">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
@@ -25834,7 +26168,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AI61"/>
+  <dimension ref="A1:AI62"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="11" customWidth="1"/>
@@ -25869,22 +26203,22 @@
   <sheetData>
     <row r="1" spans="1:35" s="5" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="25" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>11</v>
@@ -25914,7 +26248,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="14.1" customHeight="1">
@@ -25989,28 +26323,28 @@
         <v>1</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V3" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" s="30" t="s">
         <v>18</v>
       </c>
       <c r="X3" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA3" s="24">
         <v>44561</v>
@@ -29142,6 +29476,56 @@
       </c>
       <c r="P61" s="9">
         <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="12.75">
+      <c r="A62" s="12">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="13">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="13">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="14">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="14">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="14">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="14">
+        <v>-273879.41101316386</v>
+      </c>
+      <c r="H62" s="15">
+        <v>-219983.46181863532</v>
+      </c>
+      <c r="I62" s="15">
+        <v>12844910.977422856</v>
+      </c>
+      <c r="J62" s="15">
+        <v>15991914.228140764</v>
+      </c>
+      <c r="K62" s="15">
+        <v>8864712.2860347666</v>
+      </c>
+      <c r="L62" s="15">
+        <v>16990140.268494405</v>
+      </c>
+      <c r="M62" s="15">
+        <v>8125427.9824596383</v>
+      </c>
+      <c r="N62" s="14">
+        <v>998226.04035364126</v>
+      </c>
+      <c r="O62" s="9">
+        <v>107.7933992308817</v>
+      </c>
+      <c r="P62" s="9">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>
